--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91868</v>
+        <v>91873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B7" t="n">
-        <v>95861</v>
+        <v>92830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,34 +1200,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R7" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1271,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>95868</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,37 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R8" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>88755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88755</v>
+        <v>92830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>92830</v>
+        <v>95868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,37 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R7" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>95868</v>
+        <v>92830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R8" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91873</v>
+        <v>91877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>88759</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>88759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128853032</v>
+        <v>128853021</v>
       </c>
       <c r="B2" t="n">
         <v>91508</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436468</v>
+        <v>436522</v>
       </c>
       <c r="R2" t="n">
-        <v>7004427</v>
+        <v>7004274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128853021</v>
+        <v>128853032</v>
       </c>
       <c r="B3" t="n">
         <v>91508</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436522</v>
+        <v>436468</v>
       </c>
       <c r="R3" t="n">
-        <v>7004274</v>
+        <v>7004427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>88759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88759</v>
+        <v>92834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128853021</v>
+        <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436522</v>
+        <v>436468</v>
       </c>
       <c r="R2" t="n">
-        <v>7004274</v>
+        <v>7004427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128853032</v>
+        <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436468</v>
+        <v>436522</v>
       </c>
       <c r="R3" t="n">
-        <v>7004427</v>
+        <v>7004274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91877</v>
+        <v>91882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>88759</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>88764</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>88771</v>
+        <v>88774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128853019</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128853027</v>
       </c>
       <c r="B8" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91893</v>
+        <v>91896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>88777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88774</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>92852</v>
+        <v>95895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,37 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R7" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>95892</v>
+        <v>92855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R8" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>88777</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>88777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B7" t="n">
-        <v>95895</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,34 +1200,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R7" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1271,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B8" t="n">
-        <v>92855</v>
+        <v>95895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,37 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R8" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>95895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,37 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R7" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>95895</v>
+        <v>92855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R8" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>88777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88777</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128853032</v>
+        <v>128853021</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436468</v>
+        <v>436522</v>
       </c>
       <c r="R2" t="n">
-        <v>7004427</v>
+        <v>7004274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128853021</v>
+        <v>128853032</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436522</v>
+        <v>436468</v>
       </c>
       <c r="R3" t="n">
-        <v>7004274</v>
+        <v>7004427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91896</v>
+        <v>91903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>88777</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>88781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B7" t="n">
-        <v>95895</v>
+        <v>92862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,34 +1200,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R7" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1271,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B8" t="n">
-        <v>92855</v>
+        <v>95905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,37 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R8" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853021</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853032</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91903</v>
+        <v>91910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>88788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88781</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>128853019</v>
       </c>
       <c r="B7" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128853027</v>
       </c>
       <c r="B8" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853021</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853032</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>88788</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>88790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>95914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,37 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R7" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>95912</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R8" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128853021</v>
+        <v>128853032</v>
       </c>
       <c r="B2" t="n">
         <v>91542</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436522</v>
+        <v>436468</v>
       </c>
       <c r="R2" t="n">
-        <v>7004274</v>
+        <v>7004427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128853032</v>
+        <v>128853021</v>
       </c>
       <c r="B3" t="n">
         <v>91542</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436468</v>
+        <v>436522</v>
       </c>
       <c r="R3" t="n">
-        <v>7004427</v>
+        <v>7004274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B7" t="n">
-        <v>95914</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,34 +1200,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R7" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1271,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>95914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,37 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R8" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>88790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88790</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B5" t="n">
-        <v>88790</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>88791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853019</v>
+        <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>95940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,37 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436522</v>
+        <v>436498</v>
       </c>
       <c r="R7" t="n">
-        <v>7004274</v>
+        <v>7004275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853027</v>
+        <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>95914</v>
+        <v>92857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436498</v>
+        <v>436522</v>
       </c>
       <c r="R8" t="n">
-        <v>7004275</v>
+        <v>7004274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91921</v>
+        <v>91922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853013</v>
+        <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>88791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436512</v>
+        <v>436487</v>
       </c>
       <c r="R5" t="n">
-        <v>7004300</v>
+        <v>7004312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853015</v>
+        <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>88791</v>
+        <v>92858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436487</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>7004312</v>
+        <v>7004300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,14 +1723,10 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -1192,7 +1192,7 @@
         <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128853032</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128853021</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128853023</v>
       </c>
       <c r="B4" t="n">
-        <v>91922</v>
+        <v>91925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128853015</v>
       </c>
       <c r="B5" t="n">
-        <v>88791</v>
+        <v>88794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128853013</v>
       </c>
       <c r="B6" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128853027</v>
       </c>
       <c r="B7" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128853019</v>
       </c>
       <c r="B8" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>128853025</v>
       </c>
       <c r="B9" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128853035</v>
       </c>
       <c r="B10" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128853029</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128853017</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128853032</v>
+        <v>128853021</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436468</v>
+        <v>436522</v>
       </c>
       <c r="R2" t="n">
-        <v>7004427</v>
+        <v>7004274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128853021</v>
+        <v>128853029</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436522</v>
+        <v>436476</v>
       </c>
       <c r="R3" t="n">
-        <v>7004274</v>
+        <v>7004347</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128853023</v>
+        <v>128853032</v>
       </c>
       <c r="B4" t="n">
-        <v>91925</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436522</v>
+        <v>436468</v>
       </c>
       <c r="R4" t="n">
-        <v>7004274</v>
+        <v>7004427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128853015</v>
+        <v>128853023</v>
       </c>
       <c r="B5" t="n">
-        <v>88794</v>
+        <v>92292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436487</v>
+        <v>436522</v>
       </c>
       <c r="R5" t="n">
-        <v>7004312</v>
+        <v>7004274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128853013</v>
+        <v>128853027</v>
       </c>
       <c r="B6" t="n">
-        <v>92861</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436512</v>
+        <v>436498</v>
       </c>
       <c r="R6" t="n">
-        <v>7004300</v>
+        <v>7004275</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128853027</v>
+        <v>128853015</v>
       </c>
       <c r="B7" t="n">
-        <v>95946</v>
+        <v>89143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>4405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436498</v>
+        <v>436487</v>
       </c>
       <c r="R7" t="n">
-        <v>7004275</v>
+        <v>7004312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128853019</v>
+        <v>128853035</v>
       </c>
       <c r="B8" t="n">
-        <v>92861</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,37 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436522</v>
+        <v>436455</v>
       </c>
       <c r="R8" t="n">
-        <v>7004274</v>
+        <v>7004094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1366,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1397,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128853025</v>
+        <v>128853013</v>
       </c>
       <c r="B9" t="n">
-        <v>83011</v>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1400,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436498</v>
+        <v>436512</v>
       </c>
       <c r="R9" t="n">
-        <v>7004275</v>
+        <v>7004300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,6 +1471,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1499,45 +1495,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128853035</v>
+        <v>128853019</v>
       </c>
       <c r="B10" t="n">
-        <v>92498</v>
+        <v>93233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436455</v>
+        <v>436522</v>
       </c>
       <c r="R10" t="n">
-        <v>7004094</v>
+        <v>7004274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,6 +1577,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128853029</v>
+        <v>128853025</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,21 +1612,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436476</v>
+        <v>436498</v>
       </c>
       <c r="R11" t="n">
-        <v>7004347</v>
+        <v>7004275</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,104 +1700,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>128853017</v>
-      </c>
-      <c r="B12" t="n">
-        <v>91563</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Mårdsundsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>436495</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7004325</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Örtrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47944-2025 artfynd.xlsx
+++ b/artfynd/A 47944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853027</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853015</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853035</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853013</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853019</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,8 +1750,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128853025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>